--- a/Result/profitability/5212.xlsx
+++ b/Result/profitability/5212.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.02</v>
       </c>
       <c r="M2" t="n">
-        <v>0.81375</v>
+        <v>0.795</v>
       </c>
       <c r="N2" t="n">
-        <v>49.94</v>
+        <v>49.54375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.9</v>
       </c>
       <c r="M3" t="n">
-        <v>0.54375</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>47.67375</v>
+        <v>48.43125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3962499999999999</v>
+        <v>0.475</v>
       </c>
       <c r="N4" t="n">
-        <v>47.4425</v>
+        <v>48.415</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>3.09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7224999999999999</v>
+        <v>0.91625</v>
       </c>
       <c r="N5" t="n">
-        <v>48.55875</v>
+        <v>49.0275</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-1.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.63625</v>
+        <v>0.42625</v>
       </c>
       <c r="N6" t="n">
-        <v>46.12</v>
+        <v>46.22</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0.21875</v>
+        <v>0.1175</v>
       </c>
       <c r="N7" t="n">
-        <v>44.17749999999999</v>
+        <v>44.3325</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.11</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03500000000000002</v>
+        <v>0.03625000000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>43.68</v>
+        <v>44.6825</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.86</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004999999999999977</v>
+        <v>0.005000000000000004</v>
       </c>
       <c r="N9" t="n">
         <v>43.55875</v>
@@ -1645,7 +1645,7 @@
         <v>-1.03</v>
       </c>
       <c r="M10" t="n">
-        <v>0.003749999999999976</v>
+        <v>0.003750000000000003</v>
       </c>
       <c r="N10" t="n">
         <v>44.72125</v>
@@ -1772,7 +1772,7 @@
         <v>-0.58</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04374999999999998</v>
+        <v>0.04375000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>45.74125</v>
@@ -1899,7 +1899,7 @@
         <v>-0.17</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04749999999999997</v>
+        <v>0.0475</v>
       </c>
       <c r="N12" t="n">
         <v>46.3775</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>253</v>
+      </c>
+      <c r="D75" t="n">
+        <v>115</v>
+      </c>
+      <c r="E75" t="n">
+        <v>139</v>
+      </c>
+      <c r="F75" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="G75" t="n">
+        <v>46</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.12%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>44</v>
+      </c>
+      <c r="K75" t="n">
+        <v>38</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N75" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.020000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1715508021390375</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.522727272727273</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07350058800470394</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
